--- a/DBs/nfl/Results/NFL_2018_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2018_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerProjects2\NFL_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\nfl\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5431DC32-A976-4C4D-AB4E-4BD8A084C48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2581AC6E-2271-40BD-94BA-6C348313B444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{633FB283-8748-4509-A0F6-EFB7FE49C3ED}"/>
   </bookViews>
@@ -121,9 +121,6 @@
     <t>KC</t>
   </si>
   <si>
-    <t>SD</t>
-  </si>
-  <si>
     <t>CAR</t>
   </si>
   <si>
@@ -154,9 +151,6 @@
     <t>DET</t>
   </si>
   <si>
-    <t>STL</t>
-  </si>
-  <si>
     <t>OAK</t>
   </si>
   <si>
@@ -176,6 +170,12 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>LAR</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1648,7 @@
         <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -1677,7 +1677,7 @@
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F21" t="s">
         <v>32</v>
@@ -1709,10 +1709,10 @@
         <v>11</v>
       </c>
       <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
         <v>34</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
@@ -1741,10 +1741,10 @@
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1773,10 +1773,10 @@
         <v>11</v>
       </c>
       <c r="E24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" t="s">
         <v>36</v>
-      </c>
-      <c r="F24" t="s">
-        <v>37</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
@@ -1805,10 +1805,10 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
@@ -1837,10 +1837,10 @@
         <v>11</v>
       </c>
       <c r="E26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" t="s">
         <v>38</v>
-      </c>
-      <c r="F26" t="s">
-        <v>39</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
@@ -1869,10 +1869,10 @@
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1901,10 +1901,10 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" t="s">
         <v>40</v>
-      </c>
-      <c r="F28" t="s">
-        <v>41</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
@@ -1933,10 +1933,10 @@
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
@@ -1965,10 +1965,10 @@
         <v>11</v>
       </c>
       <c r="E30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" t="s">
         <v>42</v>
-      </c>
-      <c r="F30" t="s">
-        <v>43</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
@@ -1997,10 +1997,10 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G31" t="s">
         <v>14</v>
@@ -2029,10 +2029,10 @@
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
@@ -2061,10 +2061,10 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G33" t="s">
         <v>14</v>
@@ -2160,7 +2160,7 @@
         <v>13</v>
       </c>
       <c r="F36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G36" t="s">
         <v>14</v>
@@ -2189,7 +2189,7 @@
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F37" t="s">
         <v>13</v>
@@ -2221,7 +2221,7 @@
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F38" t="s">
         <v>17</v>
@@ -2256,7 +2256,7 @@
         <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G39" t="s">
         <v>14</v>
@@ -2352,7 +2352,7 @@
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
@@ -2381,7 +2381,7 @@
         <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F43" t="s">
         <v>19</v>
@@ -2416,7 +2416,7 @@
         <v>28</v>
       </c>
       <c r="F44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
@@ -2445,7 +2445,7 @@
         <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -2608,7 +2608,7 @@
         <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
@@ -2637,7 +2637,7 @@
         <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
@@ -2733,10 +2733,10 @@
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G54" t="s">
         <v>14</v>
@@ -2765,10 +2765,10 @@
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F55" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G55" t="s">
         <v>15</v>
@@ -2800,7 +2800,7 @@
         <v>29</v>
       </c>
       <c r="F56" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G56" t="s">
         <v>14</v>
@@ -2829,7 +2829,7 @@
         <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F57" t="s">
         <v>29</v>
@@ -2861,10 +2861,10 @@
         <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F58" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G58" t="s">
         <v>14</v>
@@ -2893,10 +2893,10 @@
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F59" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G59" t="s">
         <v>15</v>
@@ -2989,7 +2989,7 @@
         <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F62" t="s">
         <v>25</v>
@@ -3024,7 +3024,7 @@
         <v>25</v>
       </c>
       <c r="F63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G63" t="s">
         <v>15</v>
@@ -3053,10 +3053,10 @@
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F64" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G64" t="s">
         <v>14</v>
@@ -3085,10 +3085,10 @@
         <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G65" t="s">
         <v>15</v>
@@ -3120,7 +3120,7 @@
         <v>21</v>
       </c>
       <c r="F66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G66" t="s">
         <v>14</v>
@@ -3149,7 +3149,7 @@
         <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F67" t="s">
         <v>21</v>
@@ -3309,7 +3309,7 @@
         <v>11</v>
       </c>
       <c r="E72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F72" t="s">
         <v>18</v>
@@ -3344,7 +3344,7 @@
         <v>18</v>
       </c>
       <c r="F73" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G73" t="s">
         <v>15</v>
@@ -3440,7 +3440,7 @@
         <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G76" t="s">
         <v>14</v>
@@ -3469,7 +3469,7 @@
         <v>11</v>
       </c>
       <c r="E77" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F77" t="s">
         <v>16</v>
@@ -3501,10 +3501,10 @@
         <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G78" t="s">
         <v>14</v>
@@ -3533,10 +3533,10 @@
         <v>11</v>
       </c>
       <c r="E79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F79" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
@@ -3760,7 +3760,7 @@
         <v>26</v>
       </c>
       <c r="F86" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G86" t="s">
         <v>14</v>
@@ -3789,7 +3789,7 @@
         <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F87" t="s">
         <v>26</v>
@@ -3821,10 +3821,10 @@
         <v>11</v>
       </c>
       <c r="E88" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F88" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G88" t="s">
         <v>14</v>
@@ -3853,10 +3853,10 @@
         <v>11</v>
       </c>
       <c r="E89" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F89" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G89" t="s">
         <v>15</v>
@@ -3885,10 +3885,10 @@
         <v>11</v>
       </c>
       <c r="E90" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F90" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G90" t="s">
         <v>15</v>
@@ -3917,10 +3917,10 @@
         <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F91" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G91" t="s">
         <v>14</v>
@@ -3949,10 +3949,10 @@
         <v>11</v>
       </c>
       <c r="E92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F92" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G92" t="s">
         <v>14</v>
@@ -3981,10 +3981,10 @@
         <v>11</v>
       </c>
       <c r="E93" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G93" t="s">
         <v>15</v>
@@ -4013,7 +4013,7 @@
         <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F94" t="s">
         <v>22</v>
@@ -4048,7 +4048,7 @@
         <v>22</v>
       </c>
       <c r="F95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
@@ -4141,7 +4141,7 @@
         <v>11</v>
       </c>
       <c r="E98" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -4176,7 +4176,7 @@
         <v>28</v>
       </c>
       <c r="F99" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G99" t="s">
         <v>15</v>
@@ -4269,7 +4269,7 @@
         <v>11</v>
       </c>
       <c r="E102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F102" t="s">
         <v>17</v>
@@ -4304,7 +4304,7 @@
         <v>17</v>
       </c>
       <c r="F103" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
@@ -4333,7 +4333,7 @@
         <v>11</v>
       </c>
       <c r="E104" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F104" t="s">
         <v>30</v>
@@ -4368,7 +4368,7 @@
         <v>30</v>
       </c>
       <c r="F105" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G105" t="s">
         <v>15</v>
@@ -4461,10 +4461,10 @@
         <v>11</v>
       </c>
       <c r="E108" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F108" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G108" t="s">
         <v>14</v>
@@ -4493,10 +4493,10 @@
         <v>11</v>
       </c>
       <c r="E109" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F109" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G109" t="s">
         <v>15</v>
@@ -4528,7 +4528,7 @@
         <v>24</v>
       </c>
       <c r="F110" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G110" t="s">
         <v>14</v>
@@ -4557,7 +4557,7 @@
         <v>11</v>
       </c>
       <c r="E111" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F111" t="s">
         <v>24</v>
@@ -4717,7 +4717,7 @@
         <v>11</v>
       </c>
       <c r="E116" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F116" t="s">
         <v>21</v>
@@ -4752,7 +4752,7 @@
         <v>21</v>
       </c>
       <c r="F117" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G117" t="s">
         <v>15</v>
@@ -4781,10 +4781,10 @@
         <v>11</v>
       </c>
       <c r="E118" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F118" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G118" t="s">
         <v>15</v>
@@ -4813,10 +4813,10 @@
         <v>11</v>
       </c>
       <c r="E119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F119" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G119" t="s">
         <v>14</v>
@@ -4909,7 +4909,7 @@
         <v>11</v>
       </c>
       <c r="E122" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F122" t="s">
         <v>29</v>
@@ -4944,7 +4944,7 @@
         <v>29</v>
       </c>
       <c r="F123" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G123" t="s">
         <v>15</v>
@@ -5040,7 +5040,7 @@
         <v>32</v>
       </c>
       <c r="F126" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G126" t="s">
         <v>15</v>
@@ -5069,7 +5069,7 @@
         <v>11</v>
       </c>
       <c r="E127" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F127" t="s">
         <v>32</v>
@@ -5165,7 +5165,7 @@
         <v>11</v>
       </c>
       <c r="E130" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F130" t="s">
         <v>25</v>
@@ -5200,7 +5200,7 @@
         <v>25</v>
       </c>
       <c r="F131" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G131" t="s">
         <v>15</v>
@@ -5485,10 +5485,10 @@
         <v>11</v>
       </c>
       <c r="E140" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F140" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G140" t="s">
         <v>14</v>
@@ -5517,10 +5517,10 @@
         <v>11</v>
       </c>
       <c r="E141" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F141" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G141" t="s">
         <v>15</v>
@@ -5549,10 +5549,10 @@
         <v>11</v>
       </c>
       <c r="E142" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F142" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G142" t="s">
         <v>14</v>
@@ -5581,10 +5581,10 @@
         <v>11</v>
       </c>
       <c r="E143" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F143" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G143" t="s">
         <v>15</v>
@@ -5677,10 +5677,10 @@
         <v>11</v>
       </c>
       <c r="E146" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F146" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G146" t="s">
         <v>14</v>
@@ -5709,10 +5709,10 @@
         <v>11</v>
       </c>
       <c r="E147" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F147" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G147" t="s">
         <v>15</v>
@@ -5741,7 +5741,7 @@
         <v>11</v>
       </c>
       <c r="E148" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F148" t="s">
         <v>29</v>
@@ -5776,7 +5776,7 @@
         <v>29</v>
       </c>
       <c r="F149" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G149" t="s">
         <v>14</v>
@@ -5869,10 +5869,10 @@
         <v>11</v>
       </c>
       <c r="E152" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F152" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G152" t="s">
         <v>15</v>
@@ -5901,10 +5901,10 @@
         <v>11</v>
       </c>
       <c r="E153" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F153" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G153" t="s">
         <v>14</v>
@@ -5936,7 +5936,7 @@
         <v>23</v>
       </c>
       <c r="F154" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G154" t="s">
         <v>14</v>
@@ -5965,7 +5965,7 @@
         <v>11</v>
       </c>
       <c r="E155" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F155" t="s">
         <v>23</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="F156" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G156" t="s">
         <v>14</v>
@@ -6029,7 +6029,7 @@
         <v>11</v>
       </c>
       <c r="E157" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F157" t="s">
         <v>31</v>
@@ -6125,10 +6125,10 @@
         <v>11</v>
       </c>
       <c r="E160" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F160" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G160" t="s">
         <v>14</v>
@@ -6157,10 +6157,10 @@
         <v>11</v>
       </c>
       <c r="E161" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F161" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G161" t="s">
         <v>15</v>
@@ -6192,7 +6192,7 @@
         <v>26</v>
       </c>
       <c r="F162" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G162" t="s">
         <v>14</v>
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="E163" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F163" t="s">
         <v>26</v>
@@ -6445,7 +6445,7 @@
         <v>11</v>
       </c>
       <c r="E170" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F170" t="s">
         <v>21</v>
@@ -6480,7 +6480,7 @@
         <v>21</v>
       </c>
       <c r="F171" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G171" t="s">
         <v>14</v>
@@ -6509,7 +6509,7 @@
         <v>11</v>
       </c>
       <c r="E172" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F172" t="s">
         <v>19</v>
@@ -6544,7 +6544,7 @@
         <v>19</v>
       </c>
       <c r="F173" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G173" t="s">
         <v>15</v>
@@ -6576,7 +6576,7 @@
         <v>28</v>
       </c>
       <c r="F174" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G174" t="s">
         <v>14</v>
@@ -6605,7 +6605,7 @@
         <v>11</v>
       </c>
       <c r="E175" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -6637,10 +6637,10 @@
         <v>11</v>
       </c>
       <c r="E176" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F176" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G176" t="s">
         <v>15</v>
@@ -6669,10 +6669,10 @@
         <v>11</v>
       </c>
       <c r="E177" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F177" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G177" t="s">
         <v>14</v>
@@ -6701,10 +6701,10 @@
         <v>11</v>
       </c>
       <c r="E178" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F178" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G178" t="s">
         <v>15</v>
@@ -6733,10 +6733,10 @@
         <v>11</v>
       </c>
       <c r="E179" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F179" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G179" t="s">
         <v>14</v>
@@ -6765,7 +6765,7 @@
         <v>11</v>
       </c>
       <c r="E180" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F180" t="s">
         <v>24</v>
@@ -6800,7 +6800,7 @@
         <v>24</v>
       </c>
       <c r="F181" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G181" t="s">
         <v>15</v>
@@ -6957,7 +6957,7 @@
         <v>11</v>
       </c>
       <c r="E186" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F186" t="s">
         <v>29</v>
@@ -6992,7 +6992,7 @@
         <v>29</v>
       </c>
       <c r="F187" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G187" t="s">
         <v>15</v>
@@ -7021,10 +7021,10 @@
         <v>11</v>
       </c>
       <c r="E188" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F188" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G188" t="s">
         <v>15</v>
@@ -7053,10 +7053,10 @@
         <v>11</v>
       </c>
       <c r="E189" t="s">
+        <v>36</v>
+      </c>
+      <c r="F189" t="s">
         <v>37</v>
-      </c>
-      <c r="F189" t="s">
-        <v>38</v>
       </c>
       <c r="G189" t="s">
         <v>14</v>
@@ -7085,7 +7085,7 @@
         <v>11</v>
       </c>
       <c r="E190" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F190" t="s">
         <v>27</v>
@@ -7120,7 +7120,7 @@
         <v>27</v>
       </c>
       <c r="F191" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G191" t="s">
         <v>15</v>
@@ -7149,7 +7149,7 @@
         <v>11</v>
       </c>
       <c r="E192" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F192" t="s">
         <v>12</v>
@@ -7184,7 +7184,7 @@
         <v>12</v>
       </c>
       <c r="F193" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G193" t="s">
         <v>14</v>
@@ -7216,7 +7216,7 @@
         <v>22</v>
       </c>
       <c r="F194" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G194" t="s">
         <v>15</v>
@@ -7245,7 +7245,7 @@
         <v>11</v>
       </c>
       <c r="E195" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F195" t="s">
         <v>22</v>
@@ -7277,7 +7277,7 @@
         <v>11</v>
       </c>
       <c r="E196" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F196" t="s">
         <v>26</v>
@@ -7312,7 +7312,7 @@
         <v>26</v>
       </c>
       <c r="F197" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G197" t="s">
         <v>14</v>
@@ -7536,7 +7536,7 @@
         <v>28</v>
       </c>
       <c r="F204" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G204" t="s">
         <v>15</v>
@@ -7565,7 +7565,7 @@
         <v>11</v>
       </c>
       <c r="E205" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -7661,10 +7661,10 @@
         <v>11</v>
       </c>
       <c r="E208" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F208" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G208" t="s">
         <v>14</v>
@@ -7693,10 +7693,10 @@
         <v>11</v>
       </c>
       <c r="E209" t="s">
+        <v>34</v>
+      </c>
+      <c r="F209" t="s">
         <v>35</v>
-      </c>
-      <c r="F209" t="s">
-        <v>36</v>
       </c>
       <c r="G209" t="s">
         <v>15</v>
@@ -7725,7 +7725,7 @@
         <v>11</v>
       </c>
       <c r="E210" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F210" t="s">
         <v>29</v>
@@ -7760,7 +7760,7 @@
         <v>29</v>
       </c>
       <c r="F211" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G211" t="s">
         <v>14</v>
@@ -8045,7 +8045,7 @@
         <v>11</v>
       </c>
       <c r="E220" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F220" t="s">
         <v>16</v>
@@ -8080,7 +8080,7 @@
         <v>16</v>
       </c>
       <c r="F221" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G221" t="s">
         <v>15</v>
@@ -8109,10 +8109,10 @@
         <v>11</v>
       </c>
       <c r="E222" t="s">
+        <v>40</v>
+      </c>
+      <c r="F222" t="s">
         <v>41</v>
-      </c>
-      <c r="F222" t="s">
-        <v>42</v>
       </c>
       <c r="G222" t="s">
         <v>14</v>
@@ -8141,10 +8141,10 @@
         <v>11</v>
       </c>
       <c r="E223" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F223" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G223" t="s">
         <v>15</v>
@@ -8173,10 +8173,10 @@
         <v>11</v>
       </c>
       <c r="E224" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F224" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G224" t="s">
         <v>15</v>
@@ -8205,10 +8205,10 @@
         <v>11</v>
       </c>
       <c r="E225" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F225" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G225" t="s">
         <v>14</v>
@@ -8368,7 +8368,7 @@
         <v>32</v>
       </c>
       <c r="F230" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G230" t="s">
         <v>14</v>
@@ -8397,7 +8397,7 @@
         <v>11</v>
       </c>
       <c r="E231" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F231" t="s">
         <v>32</v>
@@ -8429,7 +8429,7 @@
         <v>11</v>
       </c>
       <c r="E232" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F232" t="s">
         <v>25</v>
@@ -8464,7 +8464,7 @@
         <v>25</v>
       </c>
       <c r="F233" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G233" t="s">
         <v>14</v>
@@ -8496,7 +8496,7 @@
         <v>19</v>
       </c>
       <c r="F234" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G234" t="s">
         <v>15</v>
@@ -8525,7 +8525,7 @@
         <v>11</v>
       </c>
       <c r="E235" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F235" t="s">
         <v>19</v>
@@ -8557,10 +8557,10 @@
         <v>11</v>
       </c>
       <c r="E236" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F236" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G236" t="s">
         <v>14</v>
@@ -8589,10 +8589,10 @@
         <v>11</v>
       </c>
       <c r="E237" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F237" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G237" t="s">
         <v>15</v>
@@ -8621,7 +8621,7 @@
         <v>11</v>
       </c>
       <c r="E238" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F238" t="s">
         <v>29</v>
@@ -8656,7 +8656,7 @@
         <v>29</v>
       </c>
       <c r="F239" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G239" t="s">
         <v>15</v>
@@ -8816,7 +8816,7 @@
         <v>29</v>
       </c>
       <c r="F244" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G244" t="s">
         <v>14</v>
@@ -8845,7 +8845,7 @@
         <v>11</v>
       </c>
       <c r="E245" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F245" t="s">
         <v>29</v>
@@ -8880,7 +8880,7 @@
         <v>13</v>
       </c>
       <c r="F246" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G246" t="s">
         <v>15</v>
@@ -8909,7 +8909,7 @@
         <v>11</v>
       </c>
       <c r="E247" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F247" t="s">
         <v>13</v>
@@ -8941,7 +8941,7 @@
         <v>11</v>
       </c>
       <c r="E248" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F248" t="s">
         <v>30</v>
@@ -8976,7 +8976,7 @@
         <v>30</v>
       </c>
       <c r="F249" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G249" t="s">
         <v>15</v>
@@ -9008,7 +9008,7 @@
         <v>28</v>
       </c>
       <c r="F250" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G250" t="s">
         <v>14</v>
@@ -9037,7 +9037,7 @@
         <v>11</v>
       </c>
       <c r="E251" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -9133,7 +9133,7 @@
         <v>11</v>
       </c>
       <c r="E254" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F254" t="s">
         <v>17</v>
@@ -9168,7 +9168,7 @@
         <v>17</v>
       </c>
       <c r="F255" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G255" t="s">
         <v>14</v>
@@ -9264,7 +9264,7 @@
         <v>26</v>
       </c>
       <c r="F258" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G258" t="s">
         <v>14</v>
@@ -9293,7 +9293,7 @@
         <v>11</v>
       </c>
       <c r="E259" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F259" t="s">
         <v>26</v>
@@ -9325,10 +9325,10 @@
         <v>11</v>
       </c>
       <c r="E260" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F260" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G260" t="s">
         <v>15</v>
@@ -9357,10 +9357,10 @@
         <v>11</v>
       </c>
       <c r="E261" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F261" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G261" t="s">
         <v>14</v>
@@ -9392,7 +9392,7 @@
         <v>23</v>
       </c>
       <c r="F262" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G262" t="s">
         <v>15</v>
@@ -9421,7 +9421,7 @@
         <v>11</v>
       </c>
       <c r="E263" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F263" t="s">
         <v>23</v>
@@ -9456,7 +9456,7 @@
         <v>31</v>
       </c>
       <c r="F264" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G264" t="s">
         <v>14</v>
@@ -9485,7 +9485,7 @@
         <v>11</v>
       </c>
       <c r="E265" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F265" t="s">
         <v>31</v>
@@ -9520,7 +9520,7 @@
         <v>22</v>
       </c>
       <c r="F266" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G266" t="s">
         <v>14</v>
@@ -9549,7 +9549,7 @@
         <v>11</v>
       </c>
       <c r="E267" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F267" t="s">
         <v>22</v>
@@ -9584,7 +9584,7 @@
         <v>27</v>
       </c>
       <c r="F268" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G268" t="s">
         <v>15</v>
@@ -9613,7 +9613,7 @@
         <v>11</v>
       </c>
       <c r="E269" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F269" t="s">
         <v>27</v>
@@ -9648,7 +9648,7 @@
         <v>20</v>
       </c>
       <c r="F270" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G270" t="s">
         <v>14</v>
@@ -9677,7 +9677,7 @@
         <v>11</v>
       </c>
       <c r="E271" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F271" t="s">
         <v>20</v>
@@ -9773,10 +9773,10 @@
         <v>11</v>
       </c>
       <c r="E274" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F274" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G274" t="s">
         <v>14</v>
@@ -9805,10 +9805,10 @@
         <v>11</v>
       </c>
       <c r="E275" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F275" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G275" t="s">
         <v>15</v>
@@ -9968,7 +9968,7 @@
         <v>32</v>
       </c>
       <c r="F280" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G280" t="s">
         <v>14</v>
@@ -9997,7 +9997,7 @@
         <v>11</v>
       </c>
       <c r="E281" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F281" t="s">
         <v>32</v>
@@ -10029,7 +10029,7 @@
         <v>11</v>
       </c>
       <c r="E282" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F282" t="s">
         <v>30</v>
@@ -10064,7 +10064,7 @@
         <v>30</v>
       </c>
       <c r="F283" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G283" t="s">
         <v>14</v>
@@ -10096,7 +10096,7 @@
         <v>17</v>
       </c>
       <c r="F284" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G284" t="s">
         <v>15</v>
@@ -10125,7 +10125,7 @@
         <v>11</v>
       </c>
       <c r="E285" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F285" t="s">
         <v>17</v>
@@ -10221,10 +10221,10 @@
         <v>11</v>
       </c>
       <c r="E288" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F288" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G288" t="s">
         <v>15</v>
@@ -10253,10 +10253,10 @@
         <v>11</v>
       </c>
       <c r="E289" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F289" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G289" t="s">
         <v>14</v>
@@ -10285,7 +10285,7 @@
         <v>11</v>
       </c>
       <c r="E290" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F290" t="s">
         <v>26</v>
@@ -10320,7 +10320,7 @@
         <v>26</v>
       </c>
       <c r="F291" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G291" t="s">
         <v>15</v>
@@ -10349,10 +10349,10 @@
         <v>11</v>
       </c>
       <c r="E292" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F292" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G292" t="s">
         <v>14</v>
@@ -10381,10 +10381,10 @@
         <v>11</v>
       </c>
       <c r="E293" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F293" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G293" t="s">
         <v>15</v>
@@ -10413,7 +10413,7 @@
         <v>11</v>
       </c>
       <c r="E294" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F294" t="s">
         <v>12</v>
@@ -10448,7 +10448,7 @@
         <v>12</v>
       </c>
       <c r="F295" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G295" t="s">
         <v>14</v>
@@ -10541,10 +10541,10 @@
         <v>11</v>
       </c>
       <c r="E298" t="s">
+        <v>38</v>
+      </c>
+      <c r="F298" t="s">
         <v>39</v>
-      </c>
-      <c r="F298" t="s">
-        <v>40</v>
       </c>
       <c r="G298" t="s">
         <v>14</v>
@@ -10573,10 +10573,10 @@
         <v>11</v>
       </c>
       <c r="E299" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F299" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G299" t="s">
         <v>15</v>
@@ -10605,7 +10605,7 @@
         <v>11</v>
       </c>
       <c r="E300" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F300" t="s">
         <v>13</v>
@@ -10640,7 +10640,7 @@
         <v>13</v>
       </c>
       <c r="F301" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G301" t="s">
         <v>14</v>
@@ -10669,10 +10669,10 @@
         <v>11</v>
       </c>
       <c r="E302" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F302" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G302" t="s">
         <v>14</v>
@@ -10701,10 +10701,10 @@
         <v>11</v>
       </c>
       <c r="E303" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F303" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G303" t="s">
         <v>15</v>
@@ -10864,7 +10864,7 @@
         <v>23</v>
       </c>
       <c r="F308" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G308" t="s">
         <v>15</v>
@@ -10893,7 +10893,7 @@
         <v>11</v>
       </c>
       <c r="E309" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F309" t="s">
         <v>23</v>
@@ -11053,10 +11053,10 @@
         <v>11</v>
       </c>
       <c r="E314" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F314" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G314" t="s">
         <v>15</v>
@@ -11085,10 +11085,10 @@
         <v>11</v>
       </c>
       <c r="E315" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F315" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G315" t="s">
         <v>14</v>
@@ -11117,10 +11117,10 @@
         <v>11</v>
       </c>
       <c r="E316" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F316" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G316" t="s">
         <v>15</v>
@@ -11149,10 +11149,10 @@
         <v>11</v>
       </c>
       <c r="E317" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F317" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G317" t="s">
         <v>14</v>
@@ -11245,7 +11245,7 @@
         <v>11</v>
       </c>
       <c r="E320" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -11280,7 +11280,7 @@
         <v>28</v>
       </c>
       <c r="F321" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G321" t="s">
         <v>15</v>
@@ -11309,7 +11309,7 @@
         <v>11</v>
       </c>
       <c r="E322" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F322" t="s">
         <v>32</v>
@@ -11344,7 +11344,7 @@
         <v>32</v>
       </c>
       <c r="F323" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G323" t="s">
         <v>15</v>
@@ -11373,10 +11373,10 @@
         <v>11</v>
       </c>
       <c r="E324" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F324" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G324" t="s">
         <v>15</v>
@@ -11405,10 +11405,10 @@
         <v>11</v>
       </c>
       <c r="E325" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F325" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G325" t="s">
         <v>14</v>
@@ -11437,10 +11437,10 @@
         <v>11</v>
       </c>
       <c r="E326" t="s">
+        <v>34</v>
+      </c>
+      <c r="F326" t="s">
         <v>35</v>
-      </c>
-      <c r="F326" t="s">
-        <v>36</v>
       </c>
       <c r="G326" t="s">
         <v>14</v>
@@ -11469,10 +11469,10 @@
         <v>11</v>
       </c>
       <c r="E327" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F327" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G327" t="s">
         <v>15</v>
@@ -11629,10 +11629,10 @@
         <v>11</v>
       </c>
       <c r="E332" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F332" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G332" t="s">
         <v>15</v>
@@ -11661,10 +11661,10 @@
         <v>11</v>
       </c>
       <c r="E333" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F333" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G333" t="s">
         <v>14</v>
@@ -11760,7 +11760,7 @@
         <v>22</v>
       </c>
       <c r="F336" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G336" t="s">
         <v>15</v>
@@ -11789,7 +11789,7 @@
         <v>11</v>
       </c>
       <c r="E337" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F337" t="s">
         <v>22</v>
@@ -11888,7 +11888,7 @@
         <v>16</v>
       </c>
       <c r="F340" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G340" t="s">
         <v>14</v>
@@ -11917,7 +11917,7 @@
         <v>11</v>
       </c>
       <c r="E341" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F341" t="s">
         <v>16</v>
@@ -12013,10 +12013,10 @@
         <v>11</v>
       </c>
       <c r="E344" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F344" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G344" t="s">
         <v>14</v>
@@ -12045,10 +12045,10 @@
         <v>11</v>
       </c>
       <c r="E345" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F345" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G345" t="s">
         <v>15</v>
@@ -12141,7 +12141,7 @@
         <v>11</v>
       </c>
       <c r="E348" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F348" t="s">
         <v>20</v>
@@ -12176,7 +12176,7 @@
         <v>20</v>
       </c>
       <c r="F349" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G349" t="s">
         <v>15</v>
@@ -12208,7 +12208,7 @@
         <v>28</v>
       </c>
       <c r="F350" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G350" t="s">
         <v>14</v>
@@ -12237,7 +12237,7 @@
         <v>11</v>
       </c>
       <c r="E351" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>
@@ -12333,7 +12333,7 @@
         <v>11</v>
       </c>
       <c r="E354" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F354" t="s">
         <v>31</v>
@@ -12368,7 +12368,7 @@
         <v>31</v>
       </c>
       <c r="F355" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G355" t="s">
         <v>15</v>
@@ -12528,7 +12528,7 @@
         <v>30</v>
       </c>
       <c r="F360" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G360" t="s">
         <v>14</v>
@@ -12557,7 +12557,7 @@
         <v>11</v>
       </c>
       <c r="E361" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F361" t="s">
         <v>30</v>
@@ -12592,7 +12592,7 @@
         <v>25</v>
       </c>
       <c r="F362" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G362" t="s">
         <v>14</v>
@@ -12621,7 +12621,7 @@
         <v>11</v>
       </c>
       <c r="E363" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F363" t="s">
         <v>25</v>
@@ -12653,7 +12653,7 @@
         <v>11</v>
       </c>
       <c r="E364" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F364" t="s">
         <v>18</v>
@@ -12688,7 +12688,7 @@
         <v>18</v>
       </c>
       <c r="F365" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G365" t="s">
         <v>14</v>
@@ -12845,10 +12845,10 @@
         <v>11</v>
       </c>
       <c r="E370" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F370" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G370" t="s">
         <v>15</v>
@@ -12877,10 +12877,10 @@
         <v>11</v>
       </c>
       <c r="E371" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F371" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G371" t="s">
         <v>14</v>
@@ -12909,10 +12909,10 @@
         <v>11</v>
       </c>
       <c r="E372" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F372" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G372" t="s">
         <v>15</v>
@@ -12941,10 +12941,10 @@
         <v>11</v>
       </c>
       <c r="E373" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F373" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G373" t="s">
         <v>14</v>
@@ -12976,7 +12976,7 @@
         <v>32</v>
       </c>
       <c r="F374" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G374" t="s">
         <v>15</v>
@@ -13005,7 +13005,7 @@
         <v>11</v>
       </c>
       <c r="E375" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F375" t="s">
         <v>32</v>
@@ -13040,7 +13040,7 @@
         <v>27</v>
       </c>
       <c r="F376" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G376" t="s">
         <v>14</v>
@@ -13069,7 +13069,7 @@
         <v>11</v>
       </c>
       <c r="E377" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F377" t="s">
         <v>27</v>
@@ -13165,7 +13165,7 @@
         <v>11</v>
       </c>
       <c r="E380" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F380" t="s">
         <v>29</v>
@@ -13200,7 +13200,7 @@
         <v>29</v>
       </c>
       <c r="F381" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G381" t="s">
         <v>15</v>
@@ -13229,7 +13229,7 @@
         <v>11</v>
       </c>
       <c r="E382" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F382" t="s">
         <v>20</v>
@@ -13264,7 +13264,7 @@
         <v>20</v>
       </c>
       <c r="F383" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G383" t="s">
         <v>14</v>
@@ -13296,7 +13296,7 @@
         <v>12</v>
       </c>
       <c r="F384" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G384" t="s">
         <v>14</v>
@@ -13325,7 +13325,7 @@
         <v>11</v>
       </c>
       <c r="E385" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F385" t="s">
         <v>12</v>
@@ -13421,7 +13421,7 @@
         <v>11</v>
       </c>
       <c r="E388" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F388" t="s">
         <v>13</v>
@@ -13456,7 +13456,7 @@
         <v>13</v>
       </c>
       <c r="F389" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G389" t="s">
         <v>15</v>
@@ -13485,7 +13485,7 @@
         <v>11</v>
       </c>
       <c r="E390" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F390" t="s">
         <v>17</v>
@@ -13520,7 +13520,7 @@
         <v>17</v>
       </c>
       <c r="F391" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G391" t="s">
         <v>14</v>
@@ -13552,7 +13552,7 @@
         <v>21</v>
       </c>
       <c r="F392" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G392" t="s">
         <v>14</v>
@@ -13581,7 +13581,7 @@
         <v>11</v>
       </c>
       <c r="E393" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F393" t="s">
         <v>21</v>
@@ -13872,7 +13872,7 @@
         <v>25</v>
       </c>
       <c r="F402" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G402" t="s">
         <v>15</v>
@@ -13901,7 +13901,7 @@
         <v>11</v>
       </c>
       <c r="E403" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F403" t="s">
         <v>25</v>
@@ -13933,7 +13933,7 @@
         <v>11</v>
       </c>
       <c r="E404" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F404" t="s">
         <v>18</v>
@@ -13968,7 +13968,7 @@
         <v>18</v>
       </c>
       <c r="F405" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G405" t="s">
         <v>15</v>
@@ -14000,7 +14000,7 @@
         <v>29</v>
       </c>
       <c r="F406" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G406" t="s">
         <v>14</v>
@@ -14029,7 +14029,7 @@
         <v>11</v>
       </c>
       <c r="E407" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F407" t="s">
         <v>29</v>
@@ -14061,10 +14061,10 @@
         <v>11</v>
       </c>
       <c r="E408" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F408" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G408" t="s">
         <v>15</v>
@@ -14093,10 +14093,10 @@
         <v>11</v>
       </c>
       <c r="E409" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F409" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G409" t="s">
         <v>14</v>
@@ -14125,7 +14125,7 @@
         <v>11</v>
       </c>
       <c r="E410" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F410" t="s">
         <v>12</v>
@@ -14160,7 +14160,7 @@
         <v>12</v>
       </c>
       <c r="F411" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G411" t="s">
         <v>15</v>
@@ -14189,7 +14189,7 @@
         <v>11</v>
       </c>
       <c r="E412" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F412" t="s">
         <v>20</v>
@@ -14224,7 +14224,7 @@
         <v>20</v>
       </c>
       <c r="F413" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G413" t="s">
         <v>15</v>
@@ -14253,10 +14253,10 @@
         <v>11</v>
       </c>
       <c r="E414" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F414" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G414" t="s">
         <v>14</v>
@@ -14285,10 +14285,10 @@
         <v>11</v>
       </c>
       <c r="E415" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F415" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G415" t="s">
         <v>15</v>
@@ -14317,7 +14317,7 @@
         <v>11</v>
       </c>
       <c r="E416" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F416" t="s">
         <v>28</v>
@@ -14352,7 +14352,7 @@
         <v>28</v>
       </c>
       <c r="F417" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G417" t="s">
         <v>15</v>
@@ -14381,7 +14381,7 @@
         <v>11</v>
       </c>
       <c r="E418" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F418" t="s">
         <v>32</v>
@@ -14416,7 +14416,7 @@
         <v>32</v>
       </c>
       <c r="F419" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G419" t="s">
         <v>14</v>
@@ -14448,7 +14448,7 @@
         <v>23</v>
       </c>
       <c r="F420" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G420" t="s">
         <v>15</v>
@@ -14477,7 +14477,7 @@
         <v>11</v>
       </c>
       <c r="E421" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F421" t="s">
         <v>23</v>
@@ -14512,7 +14512,7 @@
         <v>21</v>
       </c>
       <c r="F422" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G422" t="s">
         <v>15</v>
@@ -14541,7 +14541,7 @@
         <v>11</v>
       </c>
       <c r="E423" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F423" t="s">
         <v>21</v>
@@ -14576,7 +14576,7 @@
         <v>13</v>
       </c>
       <c r="F424" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G424" t="s">
         <v>14</v>
@@ -14605,7 +14605,7 @@
         <v>11</v>
       </c>
       <c r="E425" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F425" t="s">
         <v>13</v>
@@ -14640,7 +14640,7 @@
         <v>17</v>
       </c>
       <c r="F426" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G426" t="s">
         <v>14</v>
@@ -14669,7 +14669,7 @@
         <v>11</v>
       </c>
       <c r="E427" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F427" t="s">
         <v>17</v>
@@ -14701,10 +14701,10 @@
         <v>11</v>
       </c>
       <c r="E428" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F428" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G428" t="s">
         <v>14</v>
@@ -14733,10 +14733,10 @@
         <v>11</v>
       </c>
       <c r="E429" t="s">
+        <v>39</v>
+      </c>
+      <c r="F429" t="s">
         <v>40</v>
-      </c>
-      <c r="F429" t="s">
-        <v>41</v>
       </c>
       <c r="G429" t="s">
         <v>15</v>
@@ -14768,7 +14768,7 @@
         <v>18</v>
       </c>
       <c r="F430" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G430" t="s">
         <v>14</v>
@@ -14797,7 +14797,7 @@
         <v>11</v>
       </c>
       <c r="E431" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F431" t="s">
         <v>18</v>
@@ -14832,7 +14832,7 @@
         <v>19</v>
       </c>
       <c r="F432" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G432" t="s">
         <v>14</v>
@@ -14861,7 +14861,7 @@
         <v>11</v>
       </c>
       <c r="E433" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F433" t="s">
         <v>19</v>
@@ -14893,7 +14893,7 @@
         <v>11</v>
       </c>
       <c r="E434" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F434" t="s">
         <v>24</v>
@@ -14928,7 +14928,7 @@
         <v>24</v>
       </c>
       <c r="F435" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G435" t="s">
         <v>14</v>
@@ -15152,7 +15152,7 @@
         <v>29</v>
       </c>
       <c r="F442" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G442" t="s">
         <v>14</v>
@@ -15181,7 +15181,7 @@
         <v>11</v>
       </c>
       <c r="E443" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F443" t="s">
         <v>29</v>
@@ -15280,7 +15280,7 @@
         <v>12</v>
       </c>
       <c r="F446" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G446" t="s">
         <v>15</v>
@@ -15309,7 +15309,7 @@
         <v>11</v>
       </c>
       <c r="E447" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F447" t="s">
         <v>12</v>
@@ -15344,7 +15344,7 @@
         <v>31</v>
       </c>
       <c r="F448" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G448" t="s">
         <v>15</v>
@@ -15373,7 +15373,7 @@
         <v>11</v>
       </c>
       <c r="E449" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F449" t="s">
         <v>31</v>
@@ -15408,7 +15408,7 @@
         <v>27</v>
       </c>
       <c r="F450" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G450" t="s">
         <v>14</v>
@@ -15437,7 +15437,7 @@
         <v>11</v>
       </c>
       <c r="E451" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F451" t="s">
         <v>27</v>
@@ -15472,7 +15472,7 @@
         <v>16</v>
       </c>
       <c r="F452" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G452" t="s">
         <v>15</v>
@@ -15501,7 +15501,7 @@
         <v>11</v>
       </c>
       <c r="E453" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F453" t="s">
         <v>16</v>
@@ -15536,7 +15536,7 @@
         <v>13</v>
       </c>
       <c r="F454" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G454" t="s">
         <v>15</v>
@@ -15565,7 +15565,7 @@
         <v>11</v>
       </c>
       <c r="E455" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F455" t="s">
         <v>13</v>
@@ -15789,7 +15789,7 @@
         <v>11</v>
       </c>
       <c r="E462" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F462" t="s">
         <v>30</v>
@@ -15824,7 +15824,7 @@
         <v>30</v>
       </c>
       <c r="F463" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G463" t="s">
         <v>15</v>
@@ -15856,7 +15856,7 @@
         <v>28</v>
       </c>
       <c r="F464" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G464" t="s">
         <v>15</v>
@@ -15885,7 +15885,7 @@
         <v>11</v>
       </c>
       <c r="E465" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F465" t="s">
         <v>28</v>
@@ -15917,10 +15917,10 @@
         <v>11</v>
       </c>
       <c r="E466" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F466" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G466" t="s">
         <v>15</v>
@@ -15949,10 +15949,10 @@
         <v>11</v>
       </c>
       <c r="E467" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F467" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G467" t="s">
         <v>14</v>
@@ -16109,7 +16109,7 @@
         <v>11</v>
       </c>
       <c r="E472" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F472" t="s">
         <v>29</v>
@@ -16144,7 +16144,7 @@
         <v>29</v>
       </c>
       <c r="F473" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G473" t="s">
         <v>14</v>
@@ -16173,10 +16173,10 @@
         <v>11</v>
       </c>
       <c r="E474" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F474" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G474" t="s">
         <v>15</v>
@@ -16205,10 +16205,10 @@
         <v>11</v>
       </c>
       <c r="E475" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F475" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G475" t="s">
         <v>14</v>
@@ -16301,7 +16301,7 @@
         <v>11</v>
       </c>
       <c r="E478" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F478" t="s">
         <v>32</v>
@@ -16336,7 +16336,7 @@
         <v>32</v>
       </c>
       <c r="F479" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G479" t="s">
         <v>15</v>
@@ -16365,10 +16365,10 @@
         <v>11</v>
       </c>
       <c r="E480" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F480" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G480" t="s">
         <v>14</v>
@@ -16397,10 +16397,10 @@
         <v>11</v>
       </c>
       <c r="E481" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F481" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G481" t="s">
         <v>15</v>
@@ -16557,7 +16557,7 @@
         <v>11</v>
       </c>
       <c r="E486" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F486" t="s">
         <v>31</v>
@@ -16592,7 +16592,7 @@
         <v>31</v>
       </c>
       <c r="F487" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G487" t="s">
         <v>14</v>
@@ -16621,7 +16621,7 @@
         <v>11</v>
       </c>
       <c r="E488" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F488" t="s">
         <v>25</v>
@@ -16656,7 +16656,7 @@
         <v>25</v>
       </c>
       <c r="F489" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G489" t="s">
         <v>14</v>
@@ -16685,10 +16685,10 @@
         <v>11</v>
       </c>
       <c r="E490" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F490" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G490" t="s">
         <v>15</v>
@@ -16717,10 +16717,10 @@
         <v>11</v>
       </c>
       <c r="E491" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F491" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G491" t="s">
         <v>14</v>
@@ -16816,7 +16816,7 @@
         <v>22</v>
       </c>
       <c r="F494" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G494" t="s">
         <v>14</v>
@@ -16845,7 +16845,7 @@
         <v>11</v>
       </c>
       <c r="E495" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F495" t="s">
         <v>22</v>
@@ -16877,7 +16877,7 @@
         <v>11</v>
       </c>
       <c r="E496" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F496" t="s">
         <v>28</v>
@@ -16912,7 +16912,7 @@
         <v>28</v>
       </c>
       <c r="F497" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G497" t="s">
         <v>14</v>
@@ -17069,10 +17069,10 @@
         <v>11</v>
       </c>
       <c r="E502" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F502" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G502" t="s">
         <v>14</v>
@@ -17101,10 +17101,10 @@
         <v>11</v>
       </c>
       <c r="E503" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F503" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G503" t="s">
         <v>15</v>
@@ -17133,10 +17133,10 @@
         <v>11</v>
       </c>
       <c r="E504" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F504" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G504" t="s">
         <v>15</v>
@@ -17165,10 +17165,10 @@
         <v>11</v>
       </c>
       <c r="E505" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F505" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G505" t="s">
         <v>14</v>
@@ -17200,7 +17200,7 @@
         <v>32</v>
       </c>
       <c r="F506" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G506" t="s">
         <v>14</v>
@@ -17229,7 +17229,7 @@
         <v>11</v>
       </c>
       <c r="E507" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F507" t="s">
         <v>32</v>
@@ -17264,7 +17264,7 @@
         <v>12</v>
       </c>
       <c r="F508" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G508" t="s">
         <v>15</v>
@@ -17293,7 +17293,7 @@
         <v>11</v>
       </c>
       <c r="E509" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F509" t="s">
         <v>12</v>
@@ -17325,7 +17325,7 @@
         <v>11</v>
       </c>
       <c r="E510" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F510" t="s">
         <v>29</v>
@@ -17360,7 +17360,7 @@
         <v>29</v>
       </c>
       <c r="F511" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G511" t="s">
         <v>15</v>
@@ -17447,10 +17447,10 @@
         <v>2018</v>
       </c>
       <c r="C514" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D514" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E514" t="s">
         <v>19</v>
@@ -17479,10 +17479,10 @@
         <v>2018</v>
       </c>
       <c r="C515" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D515" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E515" t="s">
         <v>23</v>
@@ -17511,16 +17511,16 @@
         <v>2018</v>
       </c>
       <c r="C516" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D516" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E516" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F516" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G516" t="s">
         <v>14</v>
@@ -17543,16 +17543,16 @@
         <v>2018</v>
       </c>
       <c r="C517" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D517" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E517" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F517" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G517" t="s">
         <v>15</v>
@@ -17575,13 +17575,13 @@
         <v>2018</v>
       </c>
       <c r="C518" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D518" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E518" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F518" t="s">
         <v>16</v>
@@ -17607,16 +17607,16 @@
         <v>2018</v>
       </c>
       <c r="C519" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D519" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E519" t="s">
         <v>16</v>
       </c>
       <c r="F519" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G519" t="s">
         <v>14</v>
@@ -17639,16 +17639,16 @@
         <v>2018</v>
       </c>
       <c r="C520" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D520" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E520" t="s">
         <v>12</v>
       </c>
       <c r="F520" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G520" t="s">
         <v>15</v>
@@ -17671,13 +17671,13 @@
         <v>2018</v>
       </c>
       <c r="C521" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D521" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E521" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F521" t="s">
         <v>12</v>
@@ -17703,10 +17703,10 @@
         <v>2018</v>
       </c>
       <c r="C522" t="s">
+        <v>44</v>
+      </c>
+      <c r="D522" t="s">
         <v>46</v>
-      </c>
-      <c r="D522" t="s">
-        <v>48</v>
       </c>
       <c r="E522" t="s">
         <v>32</v>
@@ -17735,10 +17735,10 @@
         <v>2018</v>
       </c>
       <c r="C523" t="s">
+        <v>44</v>
+      </c>
+      <c r="D523" t="s">
         <v>46</v>
-      </c>
-      <c r="D523" t="s">
-        <v>48</v>
       </c>
       <c r="E523" t="s">
         <v>19</v>
@@ -17767,16 +17767,16 @@
         <v>2018</v>
       </c>
       <c r="C524" t="s">
+        <v>44</v>
+      </c>
+      <c r="D524" t="s">
         <v>46</v>
       </c>
-      <c r="D524" t="s">
-        <v>48</v>
-      </c>
       <c r="E524" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F524" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G524" t="s">
         <v>14</v>
@@ -17799,16 +17799,16 @@
         <v>2018</v>
       </c>
       <c r="C525" t="s">
+        <v>44</v>
+      </c>
+      <c r="D525" t="s">
         <v>46</v>
       </c>
-      <c r="D525" t="s">
-        <v>48</v>
-      </c>
       <c r="E525" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F525" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G525" t="s">
         <v>15</v>
@@ -17831,16 +17831,16 @@
         <v>2018</v>
       </c>
       <c r="C526" t="s">
+        <v>44</v>
+      </c>
+      <c r="D526" t="s">
         <v>46</v>
-      </c>
-      <c r="D526" t="s">
-        <v>48</v>
       </c>
       <c r="E526" t="s">
         <v>22</v>
       </c>
       <c r="F526" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G526" t="s">
         <v>14</v>
@@ -17863,13 +17863,13 @@
         <v>2018</v>
       </c>
       <c r="C527" t="s">
+        <v>44</v>
+      </c>
+      <c r="D527" t="s">
         <v>46</v>
       </c>
-      <c r="D527" t="s">
-        <v>48</v>
-      </c>
       <c r="E527" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F527" t="s">
         <v>22</v>
@@ -17895,10 +17895,10 @@
         <v>2018</v>
       </c>
       <c r="C528" t="s">
+        <v>44</v>
+      </c>
+      <c r="D528" t="s">
         <v>46</v>
-      </c>
-      <c r="D528" t="s">
-        <v>48</v>
       </c>
       <c r="E528" t="s">
         <v>31</v>
@@ -17927,10 +17927,10 @@
         <v>2018</v>
       </c>
       <c r="C529" t="s">
+        <v>44</v>
+      </c>
+      <c r="D529" t="s">
         <v>46</v>
-      </c>
-      <c r="D529" t="s">
-        <v>48</v>
       </c>
       <c r="E529" t="s">
         <v>12</v>
@@ -17959,13 +17959,13 @@
         <v>2018</v>
       </c>
       <c r="C530" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D530" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E530" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F530" t="s">
         <v>31</v>
@@ -17991,16 +17991,16 @@
         <v>2018</v>
       </c>
       <c r="C531" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D531" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E531" t="s">
         <v>31</v>
       </c>
       <c r="F531" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G531" t="s">
         <v>14</v>
@@ -18023,10 +18023,10 @@
         <v>2018</v>
       </c>
       <c r="C532" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D532" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E532" t="s">
         <v>22</v>
@@ -18055,10 +18055,10 @@
         <v>2018</v>
       </c>
       <c r="C533" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D533" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E533" t="s">
         <v>32</v>
@@ -18087,19 +18087,19 @@
         <v>2018</v>
       </c>
       <c r="C534" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D534" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E534" t="s">
         <v>22</v>
       </c>
       <c r="F534" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G534" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H534">
         <v>13</v>
@@ -18119,19 +18119,19 @@
         <v>2018</v>
       </c>
       <c r="C535" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D535" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E535" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F535" t="s">
         <v>22</v>
       </c>
       <c r="G535" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H535">
         <v>3</v>
